--- a/Book3.xlsx
+++ b/Book3.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vipjoshi\Videos\sir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17776176-E9CD-4B69-9E98-D8F9AA4CE451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0611D63F-3D8B-486B-934E-DB13E819B50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E0228488-3E22-48E5-A99A-F73B38563A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
   <si>
     <t>Emp ID</t>
   </si>
@@ -183,6 +184,9 @@
   </si>
   <si>
     <t>CountA</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>CountBlank</t>
@@ -293,6 +297,18 @@
   </si>
   <si>
     <t>RANDBETWEEN</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VLOOKUP</t>
+  </si>
+  <si>
+    <t>HLOOKUP</t>
   </si>
 </sst>
 </file>
@@ -319,7 +335,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +354,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -351,10 +373,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -374,6 +399,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,59 +747,61 @@
     <col min="8" max="8" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.08984375" customWidth="1"/>
     <col min="10" max="10" width="14.81640625" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" customWidth="1"/>
     <col min="12" max="12" width="13.453125" customWidth="1"/>
-    <col min="14" max="14" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.90625" customWidth="1"/>
+    <col min="14" max="14" width="14.08984375" customWidth="1"/>
     <col min="15" max="15" width="13.90625" customWidth="1"/>
     <col min="16" max="16" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -781,22 +809,22 @@
       <c r="A2" s="1">
         <v>101</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1">
         <v>45000</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>43845</v>
       </c>
       <c r="H2" s="1">
@@ -839,22 +867,22 @@
       <c r="A3" s="1">
         <v>102</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="1">
         <v>52000</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>44275</v>
       </c>
       <c r="H3" s="1">
@@ -864,48 +892,48 @@
         <f t="shared" ref="I3:I11" si="0">CONCATENATE(B3," ",C3)</f>
         <v>Priya Verma</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>103</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1">
         <v>61000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>43651</v>
       </c>
       <c r="H4" s="1">
@@ -948,22 +976,22 @@
       <c r="A5" s="1">
         <v>104</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1">
         <v>47000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>44785</v>
       </c>
       <c r="H5" s="1">
@@ -973,48 +1001,48 @@
         <f t="shared" si="0"/>
         <v>Neha Gupta</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>56</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1">
         <v>70000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>43191</v>
       </c>
       <c r="H6" s="1">
@@ -1057,22 +1085,22 @@
       <c r="A7" s="1">
         <v>106</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="1">
         <v>64000</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>44000</v>
       </c>
       <c r="H7" s="1">
@@ -1082,48 +1110,48 @@
         <f t="shared" si="0"/>
         <v>Pooja Shah</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="L7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="N7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="O7" s="7" t="s">
         <v>63</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>107</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="1">
         <v>56000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>44540</v>
       </c>
       <c r="H8" s="1">
@@ -1157,7 +1185,7 @@
         <f ca="1">NETWORKDAYS(G2,TODAY())</f>
         <v>1683</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="8">
         <f ca="1">TODAY()</f>
         <v>46201</v>
       </c>
@@ -1166,22 +1194,22 @@
       <c r="A9" s="1">
         <v>108</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1">
         <v>72000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>43521</v>
       </c>
       <c r="H9" s="1">
@@ -1191,45 +1219,46 @@
         <f t="shared" si="0"/>
         <v>Anjali Mishra</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L9" t="s">
+      <c r="K9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="L9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="11"/>
+      <c r="N9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P9" t="s">
+      <c r="O9" s="7" t="s">
         <v>70</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>109</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="1">
         <v>49000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>45060</v>
       </c>
       <c r="H10" s="1">
@@ -1239,26 +1268,27 @@
         <f t="shared" si="0"/>
         <v>Vikas Yadav</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <f ca="1">NOW()</f>
-        <v>46201.390119097225</v>
+        <v>46201.392450347223</v>
       </c>
       <c r="K10">
         <f>LEN(B2)</f>
         <v>5</v>
       </c>
-      <c r="L10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N10" s="9">
+      <c r="L10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="11"/>
+      <c r="N10" s="10">
         <f>PMT(10%/12,60,-H2)</f>
         <v>10623.522355634139</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="10">
         <f>IPMT(10%/12,1,60,-H2)</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="10">
         <f>PPMT(10%/12,1,60,-H2)</f>
         <v>6456.8556889674719</v>
       </c>
@@ -1267,22 +1297,22 @@
       <c r="A11" s="1">
         <v>110</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="1">
         <v>68000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>44834</v>
       </c>
       <c r="H11" s="1">
@@ -1292,20 +1322,26 @@
         <f t="shared" si="0"/>
         <v>Sneha Joshi</v>
       </c>
-      <c r="J11" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="J11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L11" t="s">
+      <c r="K11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="M11" t="s">
+      <c r="L11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N11" t="s">
+      <c r="M11" s="7" t="s">
         <v>75</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -1324,6 +1360,155 @@
       <c r="M12">
         <f>COLUMNS(A2:H11)</f>
         <v>8</v>
+      </c>
+      <c r="N12">
+        <f ca="1">RANDBETWEEN(1,100)</f>
+        <v>23</v>
+      </c>
+      <c r="O12">
+        <f>VLOOKUP(B2,Sheet2!B1:C6,2,0)</f>
+        <v>45000</v>
+      </c>
+      <c r="P12">
+        <f>HLOOKUP(B2,Sheet2!A9:F10,2,0)</f>
+        <v>45000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E0B89B-DC4E-43DD-8770-A31D6CB5FA61}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>101</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3">
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>105</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3">
+        <v>101</v>
+      </c>
+      <c r="C8" s="3">
+        <v>102</v>
+      </c>
+      <c r="D8" s="3">
+        <v>103</v>
+      </c>
+      <c r="E8" s="3">
+        <v>104</v>
+      </c>
+      <c r="F8" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>52000</v>
+      </c>
+      <c r="D10" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>47000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>70000</v>
       </c>
     </row>
   </sheetData>
